--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9373a0fbff2016bd/デスクトップ/FILES_SLN/make_the_test_on_web/make_the_test_on_web/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9373a0fbff2016bd/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{5541CF21-DF76-463B-93A9-F00AD4B4AC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1AFD348-FDFE-4EF1-9BE8-611A68C8D836}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BB11FD3-F65E-4790-BA5C-50AFA4C76DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D7D53887-9C6E-4F49-8D30-3666557B6EAC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>問題No.</t>
     <rPh sb="0" eb="2">
@@ -55,6 +55,31 @@
     <t>解答</t>
     <rPh sb="0" eb="2">
       <t>カイトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←A列は問題数の分だけ,"過不足なく"連番で埋めてください</t>
+    <rPh sb="2" eb="3">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>カフソク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>レンバン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -121,10 +146,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,11 +445,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F7CB98-675B-479F-AF32-FCDFD9CEB1C7}">
-  <dimension ref="A1:C198"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.9140625" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -446,6 +468,9 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
@@ -940,491 +965,6 @@
     <row r="101" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A138">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A139">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A140">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A141">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A143">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A144">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A146">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A147">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A148">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A149">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A150">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A151">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A152">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A153">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A154">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A155">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A156">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A157">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A158">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A159">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A160">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A161">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A163">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A164">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A165">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A166">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A167">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A168">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A169">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A170">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A171">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A173">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A174">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A175">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A176">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A177">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A178">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A179">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A180">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A181">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A183">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A184">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A185">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A186">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A187">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A188">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A189">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A190">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A191">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A192">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A193">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A194">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A195">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A196">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A197">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A198">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
